--- a/frontend/public/sample-tutorial.xlsx
+++ b/frontend/public/sample-tutorial.xlsx
@@ -397,12 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,6 +419,9 @@
       <c r="D1" t="str">
         <v>자재준비 여부</v>
       </c>
+      <c r="E1" t="str">
+        <v>자재 납기일</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -491,7 +495,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>